--- a/templates/Import reconciliation template.xlsx
+++ b/templates/Import reconciliation template.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:P1"/>
+  <dimension ref="A1:Q1"/>
   <cols>
     <col min="1" max="1" width="14.83203125" customWidth="1"/>
     <col min="2" max="2" width="14.83203125" customWidth="1"/>
@@ -411,10 +411,11 @@
     <col min="10" max="10" width="23.83203125" customWidth="1"/>
     <col min="11" max="11" width="34.83203125" customWidth="1"/>
     <col min="12" max="12" width="16.83203125" customWidth="1"/>
-    <col min="13" max="13" width="22.83203125" customWidth="1"/>
+    <col min="13" max="13" width="27.83203125" customWidth="1"/>
     <col min="14" max="14" width="22.83203125" customWidth="1"/>
-    <col min="15" max="15" width="35.83203125" customWidth="1"/>
-    <col min="16" max="16" width="28.83203125" customWidth="1"/>
+    <col min="15" max="15" width="22.83203125" customWidth="1"/>
+    <col min="16" max="16" width="35.83203125" customWidth="1"/>
+    <col min="17" max="17" width="28.83203125" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -455,21 +456,24 @@
         <v>Custom Value</v>
       </c>
       <c r="M1" t="str">
+        <v>Value for VAT (Customs)</v>
+      </c>
+      <c r="N1" t="str">
         <v>VAT as per Customs</v>
       </c>
-      <c r="N1" t="str">
+      <c r="O1" t="str">
         <v>Short Shipment (3)</v>
       </c>
-      <c r="O1" t="str">
+      <c r="P1" t="str">
         <v>Sales Reversed in the Month (4)</v>
       </c>
-      <c r="P1" t="str">
+      <c r="Q1" t="str">
         <v>Updated in Custom Report</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:P1"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:Q1"/>
   </ignoredErrors>
 </worksheet>
 </file>